--- a/Equipment.xlsx
+++ b/Equipment.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263F5EB7-4173-004E-A2F4-6A84D530BC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11780" yWindow="1120" windowWidth="29400" windowHeight="18440" xr2:uid="{D126F873-3F94-664E-876C-9F8BAD5C4AB3}"/>
+    <workbookView xWindow="480" yWindow="1760" windowWidth="29400" windowHeight="18440" xr2:uid="{D126F873-3F94-664E-876C-9F8BAD5C4AB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Input" sheetId="1" r:id="rId1"/>
